--- a/Team-Data/2007-08/3-27-2007-08.xlsx
+++ b/Team-Data/2007-08/3-27-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-2</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
@@ -754,13 +821,13 @@
         <v>6</v>
       </c>
       <c r="AI2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ2" t="n">
         <v>22</v>
       </c>
       <c r="AK2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL2" t="n">
         <v>27</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-4.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1121,7 +1188,7 @@
         <v>25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
         <v>22</v>
@@ -1148,7 +1215,7 @@
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
         <v>25</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -1571,58 +1638,58 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>0.625</v>
+        <v>0.634</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J7" t="n">
         <v>79</v>
       </c>
       <c r="K7" t="n">
-        <v>0.464</v>
+        <v>0.463</v>
       </c>
       <c r="L7" t="n">
         <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O7" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="P7" t="n">
         <v>25.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>10.8</v>
       </c>
       <c r="S7" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T7" t="n">
         <v>43.3</v>
       </c>
       <c r="U7" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V7" t="n">
         <v>13.1</v>
@@ -1631,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z7" t="n">
         <v>21.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.1</v>
+        <v>100</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
@@ -1658,28 +1725,28 @@
         <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>19</v>
       </c>
       <c r="AM7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
         <v>7</v>
@@ -1688,10 +1755,10 @@
         <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
         <v>4</v>
@@ -1709,22 +1776,22 @@
         <v>29</v>
       </c>
       <c r="AX7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY7" t="n">
         <v>8</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>22</v>
       </c>
       <c r="BA7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -1753,19 +1820,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
         <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>0.611</v>
+        <v>0.606</v>
       </c>
       <c r="H8" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I8" t="n">
         <v>39.9</v>
@@ -1792,22 +1859,22 @@
         <v>30.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R8" t="n">
         <v>11.4</v>
       </c>
       <c r="S8" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T8" t="n">
         <v>43.9</v>
       </c>
       <c r="U8" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="V8" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W8" t="n">
         <v>9.300000000000001</v>
@@ -1816,7 +1883,7 @@
         <v>6.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z8" t="n">
         <v>21</v>
@@ -1825,13 +1892,13 @@
         <v>23.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>109.6</v>
+        <v>109.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1843,7 +1910,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1873,10 +1940,10 @@
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>5</v>
@@ -1885,7 +1952,7 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1894,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ8" t="n">
         <v>16</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
         <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>0.708</v>
+        <v>0.704</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
@@ -1953,37 +2020,37 @@
         <v>36.6</v>
       </c>
       <c r="J9" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K9" t="n">
         <v>0.459</v>
       </c>
       <c r="L9" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M9" t="n">
         <v>16.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.375</v>
+        <v>0.377</v>
       </c>
       <c r="O9" t="n">
         <v>18.5</v>
       </c>
       <c r="P9" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R9" t="n">
         <v>11.7</v>
       </c>
       <c r="S9" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T9" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U9" t="n">
         <v>22.7</v>
@@ -2007,13 +2074,13 @@
         <v>19.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>97.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2025,13 +2092,13 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK9" t="n">
         <v>13</v>
@@ -2043,7 +2110,7 @@
         <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO9" t="n">
         <v>18</v>
@@ -2052,16 +2119,16 @@
         <v>20</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
         <v>27</v>
       </c>
       <c r="AT9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU9" t="n">
         <v>7</v>
@@ -2079,7 +2146,7 @@
         <v>3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
         <v>25</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
         <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>0.62</v>
+        <v>0.614</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2141,22 +2208,22 @@
         <v>0.462</v>
       </c>
       <c r="L10" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M10" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O10" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P10" t="n">
         <v>25</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R10" t="n">
         <v>12.5</v>
@@ -2168,7 +2235,7 @@
         <v>42.7</v>
       </c>
       <c r="U10" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V10" t="n">
         <v>13.2</v>
@@ -2177,13 +2244,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y10" t="n">
         <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AA10" t="n">
         <v>21.5</v>
@@ -2192,22 +2259,22 @@
         <v>111</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
         <v>1</v>
@@ -2225,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AO10" t="n">
         <v>13</v>
@@ -2246,7 +2313,7 @@
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
         <v>7</v>
@@ -2258,7 +2325,7 @@
         <v>19</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
         <v>28</v>
@@ -2270,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="BC10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>3</v>
@@ -2389,7 +2456,7 @@
         <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
         <v>14</v>
@@ -2398,7 +2465,7 @@
         <v>13</v>
       </c>
       <c r="AK11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL11" t="n">
         <v>12</v>
@@ -2416,13 +2483,13 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR11" t="n">
         <v>8</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
         <v>1</v>
@@ -2452,7 +2519,7 @@
         <v>19</v>
       </c>
       <c r="BC11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2598,7 +2665,7 @@
         <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2610,7 +2677,7 @@
         <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV12" t="n">
         <v>25</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2989,7 +3056,7 @@
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3168,7 +3235,7 @@
         <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ15" t="n">
         <v>5</v>
@@ -3177,7 +3244,7 @@
         <v>6</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16" t="n">
         <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G16" t="n">
-        <v>0.181</v>
+        <v>0.183</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="J16" t="n">
-        <v>77.7</v>
+        <v>77.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
         <v>15.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O16" t="n">
         <v>17.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.724</v>
+        <v>0.722</v>
       </c>
       <c r="R16" t="n">
         <v>9.1</v>
@@ -3257,7 +3324,7 @@
         <v>28.8</v>
       </c>
       <c r="T16" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="U16" t="n">
         <v>20.2</v>
@@ -3281,13 +3348,13 @@
         <v>20.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>92.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI16" t="n">
         <v>28</v>
@@ -3308,7 +3375,7 @@
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL16" t="n">
         <v>24</v>
@@ -3317,7 +3384,7 @@
         <v>24</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>25</v>
@@ -3326,7 +3393,7 @@
         <v>22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3341,7 +3408,7 @@
         <v>24</v>
       </c>
       <c r="AV16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW16" t="n">
         <v>17</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3532,7 +3599,7 @@
         <v>21</v>
       </c>
       <c r="AY17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ17" t="n">
         <v>20</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>27</v>
@@ -3693,10 +3760,10 @@
         <v>21</v>
       </c>
       <c r="AR18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT18" t="n">
         <v>19</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-4.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
@@ -3845,7 +3912,7 @@
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI19" t="n">
         <v>29</v>
@@ -3863,7 +3930,7 @@
         <v>18</v>
       </c>
       <c r="AN19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3875,7 +3942,7 @@
         <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS19" t="n">
         <v>13</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE20" t="n">
         <v>3</v>
@@ -4036,7 +4103,7 @@
         <v>7</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL20" t="n">
         <v>5</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-6.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4236,13 +4303,13 @@
         <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR21" t="n">
         <v>6</v>
       </c>
       <c r="AS21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT21" t="n">
         <v>15</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -4385,10 +4452,10 @@
         <v>9</v>
       </c>
       <c r="AF22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH22" t="n">
         <v>20</v>
@@ -4442,7 +4509,7 @@
         <v>26</v>
       </c>
       <c r="AY22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ22" t="n">
         <v>15</v>
@@ -4454,7 +4521,7 @@
         <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4628,13 @@
         <v>1</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>15</v>
       </c>
       <c r="AF23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG23" t="n">
         <v>16</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>4.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>7</v>
@@ -4755,10 +4822,10 @@
         <v>7</v>
       </c>
       <c r="AH24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ24" t="n">
         <v>8</v>
@@ -4791,7 +4858,7 @@
         <v>7</v>
       </c>
       <c r="AT24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4818,7 +4885,7 @@
         <v>2</v>
       </c>
       <c r="BC24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E25" t="n">
         <v>38</v>
       </c>
       <c r="F25" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>0.521</v>
+        <v>0.528</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
@@ -4865,10 +4932,10 @@
         <v>35.8</v>
       </c>
       <c r="J25" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L25" t="n">
         <v>6.5</v>
@@ -4877,19 +4944,19 @@
         <v>17.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.379</v>
+        <v>0.376</v>
       </c>
       <c r="O25" t="n">
         <v>17.6</v>
       </c>
       <c r="P25" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R25" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S25" t="n">
         <v>29.7</v>
@@ -4901,7 +4968,7 @@
         <v>21.2</v>
       </c>
       <c r="V25" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W25" t="n">
         <v>5.5</v>
@@ -4913,40 +4980,40 @@
         <v>3.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB25" t="n">
         <v>95.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH25" t="n">
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ25" t="n">
         <v>23</v>
       </c>
       <c r="AK25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
@@ -4955,7 +5022,7 @@
         <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
         <v>23</v>
@@ -4964,13 +5031,13 @@
         <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AT25" t="n">
         <v>26</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5134,7 +5201,7 @@
         <v>17</v>
       </c>
       <c r="AM26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN26" t="n">
         <v>12</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>4.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>3</v>
@@ -5301,7 +5368,7 @@
         <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI27" t="n">
         <v>26</v>
@@ -5328,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR27" t="n">
         <v>25</v>
@@ -5364,7 +5431,7 @@
         <v>24</v>
       </c>
       <c r="BC27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>29</v>
@@ -5543,7 +5610,7 @@
         <v>26</v>
       </c>
       <c r="BB28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC28" t="n">
         <v>30</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
         <v>17</v>
       </c>
       <c r="AF29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG29" t="n">
         <v>17</v>
@@ -5692,7 +5759,7 @@
         <v>30</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR29" t="n">
         <v>26</v>
@@ -5728,7 +5795,7 @@
         <v>13</v>
       </c>
       <c r="BC29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>6.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>7</v>
@@ -5889,7 +5956,7 @@
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6026,7 +6093,7 @@
         <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
         <v>2</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-27-2007-08</t>
+          <t>2008-03-27</t>
         </is>
       </c>
     </row>
